--- a/Daily_Report.xlsx
+++ b/Daily_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data_Science\01_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E4199D-3C6A-4CA2-BDF2-35E5F59C5124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3616CD-C46D-4AA1-A883-8FA20992989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -498,6 +498,12 @@
   </si>
   <si>
     <t xml:space="preserve">Functions: title, subheader, text, write, success, error, button, radio, selectbox, slider, date_input, text_input, number_input, image, columns, file_uploader, dataframe, </t>
+  </si>
+  <si>
+    <t>Python Patterns</t>
+  </si>
+  <si>
+    <t>right angle triangle pattern, inverted right angle triangle pattern, pyramid pattern, inverted pyramid, diamond, hallow sqaure, full square, right angle (number), inverted right angle traingle (number), floyds tiangle, hallow right angle trianlge, hallow pyramid, hallow diamon, haloow diamon (number), butterfly, hallow number pyrrmid, full star pyramind, inverted full star pyramid, lef aligned pyramind, right alinged pyramind.</t>
   </si>
 </sst>
 </file>
@@ -939,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="13" bestFit="1" customWidth="1"/>
@@ -1124,7 +1130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="156.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="139.19999999999999" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="156.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="139.19999999999999" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -1346,6 +1352,20 @@
       </c>
       <c r="D27" s="12" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="87" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14">
+        <v>46119</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report.xlsx
+++ b/Daily_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data_Science\01_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D884F8C-4BDF-40F4-89FE-54366CF48B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4303BC-AF66-4D46-85E9-FA3C532B2B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -51,115 +51,40 @@
     <t xml:space="preserve">Demo session -2 </t>
   </si>
   <si>
-    <t xml:space="preserve">what is name of the course  &amp; course duratation, time
-my introduction | what are main topics coverded under the course 
-who can elligible to learn this course  | what is full stack 
-list of famous llm model | course content I shared 
-scan the qr code | discussion student question and answer </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Day-1 https://youtu.be/eLFYKDISOuQ</t>
   </si>
   <si>
     <t>Day-2 https://youtu.be/Psqq3NXDBy4</t>
   </si>
   <si>
-    <t xml:space="preserve">prerequisite for this course
-talked about system configuration  | min 8gb | 512ssd | i5 processor 
-how many jobs you can apply and what job role you can apply 
-we talked job placement from 2020 - 2026 
-student question &amp; answer </t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
     <t>Demo session -3</t>
   </si>
   <si>
-    <t xml:space="preserve">Roadmap for the course (5- course roadmap)
-difference between human intellignece vs Artificial intelligence 
-Ai -- machine are mimic human behaviour is called AI 
-how Ai implement in every where -- Social median, gaming, healthcare, 
-banking sector, chatbot 
-live project == domain which is alwasy live eq - BFSI DOMAIN 
-Banking, Finance, service, insurance 
-2017-2024 _ML &amp; AI rules the world &amp; 2026- 2032 (gen ai &amp; agentic ai ) will rull 
-i showed other student placement so fare live offer of 2 student as fresher
-question and answer </t>
-  </si>
-  <si>
     <t>Day-3: https://youtu.be/LfasuLs4S4k</t>
   </si>
   <si>
     <t>Demo session - 4</t>
   </si>
   <si>
-    <t xml:space="preserve">list of project which I will session 
-what certification | how to get class notes on daily basis -- google classroom 
-what would be salary range for datascientist 
-revise few topic | question &amp; answer </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Day-4 https://youtu.be/eDPiaRlk_bc</t>
   </si>
   <si>
     <t>Demo session - 5</t>
   </si>
   <si>
-    <t xml:space="preserve">python introuce | interpreter -- excute the code line by line or bunch of code at once 
-compiler -- execute whole code at once | python accepts both interpreter &amp; compiler 
-father of pythoon - guidoe van rosam | python 1989 but to wold 2015 cuz of ds, ml, ai, agentic ai 
-python contain a rich library where you can use easily 
-python is dynamic progrmaing langag automaticaly understa inbuild datatypes 
- python is easy programing language compare to j, c, c++, .net, sql, etc 
-python is borow concept from c, java, etc, python is popwer full 
-python is no1 programin language in the world | mobile application we cant use use python | python version 3.13 | software installaiton -- anaconda, vs code </t>
-  </si>
-  <si>
     <t>Day-5 https://youtu.be/LcKRI7tGDV8</t>
   </si>
   <si>
     <t xml:space="preserve">python variable </t>
   </si>
   <si>
-    <t>world python also has name == variable ( variable == object == identifier)
-syntax ( varibale = value) variable == object &amp; value == datatypes 
-rules we discussed variable does not start with digit but end with digit 
-case sensitive | nit = 4 | nit NIT then it give errors
-special character are not allowed as variable | only _ is allowed 
-reserve words or keywords cannot be a variable  | _ mean it store previous value 
-github createsion | steps to download class notes from the googl classroom on daily base
-35 keyword | if anybody all 35 keywords pyton is complet | every keyword lot of indepth</t>
-  </si>
-  <si>
     <t>python datatypes</t>
   </si>
   <si>
-    <t xml:space="preserve">int - value without decimal | float - value with decimal only e letter is allowed | 
-e- 10 | e0 - 1 | e1- 10.0 | e2  |Boolean -- True or False 
-when you use +, - operator then it will True - 1 False - 0 
-complex -- real part &amp; imaginary part J -- SQUER ROOT OF -1 
-print() -- multiple statement | function() function without argument&amp; function with argument i just introduce this </t>
-  </si>
-  <si>
-    <t xml:space="preserve">string -- '' " " ''' ''' | '''  ''' - mutliline comments 
-string index starts with 0 | left index -- count from 0
-right index -- count from -1 
-slicing : -- all | yesterday we worked all of them </t>
-  </si>
-  <si>
     <t xml:space="preserve">python slicing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">forward slicing | backward slicing | step slicing 
-forward index | backward index 
-python type casting | other datatypes to int ( complex &amp; text string ) 
-other datatype to float ( except complex &amp; text string)  
-other datatype to bool ( no issue at all )
-student question &amp; answer we juste disccused 
-size of the bytes| scaler - vector - matrix - tensor 
-constuctore __init__ ( oops concept) </t>
   </si>
   <si>
     <t xml:space="preserve">Type casting &amp; python operators </t>
@@ -186,24 +111,10 @@
     <t xml:space="preserve">math, input() </t>
   </si>
   <si>
-    <t xml:space="preserve">framework -- collection of packages 
-packages -- collection of modules | modules - collection of function 
-function -- collection of statement 
-math module | math module many inbuild function 
-keywords - from import as | help() | input() -- bydefault give text promput
-user enter any value it will consider as string </t>
-  </si>
-  <si>
     <t xml:space="preserve">input() </t>
   </si>
   <si>
     <t xml:space="preserve">data structure </t>
-  </si>
-  <si>
-    <t xml:space="preserve">inpute() eval | we staretd working agenic ai ide 
-cursor -- clone to vs code + add on few inbuild agents
-cursor is not the free tool, specific perious it was free | more layoffs are going on 
-ai hackfest </t>
   </si>
   <si>
     <t xml:space="preserve">datat type -- user will assign one element | datastructure -- user can declare more then 1 variable 
@@ -219,40 +130,13 @@
     <t>Tuple &amp; Set</t>
   </si>
   <si>
-    <t>Tuple - immutable ( we cant change ) values once we define () 
-tuple has indexing , slicing, count will works 
-set -- {} -- dict | {1, 2, 3} -- set set function indexing &amp; slicing not allowed 
-duplicates are not allowed in set 
-add() vs append() -- add the value randomly, append the value at last 
-copy() - pop() -- remove elemnt random from set , use mention argument inside the function then it works | remove() vs discard() -- remove the elemnet from the set &amp;  discard never through an error | set opearton -- union | ,</t>
-  </si>
-  <si>
     <t>Set</t>
   </si>
   <si>
     <t xml:space="preserve">Dict &amp; Range </t>
   </si>
   <si>
-    <t xml:space="preserve">set operation -- intersection(&amp;), union(|), diffrnece(-) , symmetric differnece ^ 
-how all of them worked | symmetric difference update 
-issuperet, issubset, isdisjoint  | antigrvity agent from google  
-AGENTIC AI IDE --- cursor AI &amp; Agentic AI  
-parameter tunning -- system given parameter |Hyperparameter -- user change the system parameter as per user requirment </t>
-  </si>
-  <si>
     <t xml:space="preserve">Numpy Crash course </t>
-  </si>
-  <si>
-    <t xml:space="preserve">format of the dict is keys:values 
-keys cannot be duplicate but values can be duplicates
-dictionary is mutable |  we leared how to get keys &amp; how to value &amp; how to get items
-fromkeys(). Update() range() | range() we can pass max 3 argument 
-1st one start , end, step  | we discussed every concept of datastructure 
-numpy introduction | numpy we have many functionality 256 funcation 
-np.arange() -- arange the value betwnee the interval 
-np.arange() -- 3 argument |1d , 2d vs nd | numpy -- whihc handles nd array 
-np.zeros() -- by default flaot 0, np.ones()  bydefaul it prints float 1 | if you need integer then we must need to hypereparmeter tunning |np.random.rand (3) -- 3 random float number will generate
-np.random.randint(3) --  generate random int between 0-3 (0-, 1, 2) </t>
   </si>
   <si>
     <t xml:space="preserve">rand.randint() | how to find rows from matrix | how to get column from matrix 
@@ -360,6 +244,111 @@
   <si>
     <t>Streamlit (file_uploader, button, selectbox), PyPDF2 (PDF text extraction), Ollama LLM (chat, prompt-based resume analysis)
 Pandas (Kaggle dataset integration, job filtering), dynamic skill extraction, resume-job comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what is name of the course  &amp; course duratation | what are main topics coverded under the cours |     what is full stack | </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prerequisite for this course
+talked about system configuration  | min 8gb | 512ssd | i5 processor 
+student question &amp; answer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roadmap for the course (5- course roadmap)
+difference between human intellignece vs Artificial intelligence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">list of project | how to get class notes on daily basis -- google classroom 
+what would be salary range for datascientist 
+revise few topic | question &amp; answer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">python introuce | interpreter , compiler  | python version 3.13 | software installaiton -- anaconda, vs code </t>
+  </si>
+  <si>
+    <t>variable ( variable == object == identifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int - value without decimal | float - value with decimal only e letter is allowed | 
+e- 10 | e0 - 1 | e1- 10.0 | e2  |Boolean -- True or False 
+when you use +, - operator then it will True - 1 False - 0 
+complex -- real part &amp; imaginary part J </t>
+  </si>
+  <si>
+    <t>string -- '' " " ''' ''' | '''  ''' - mutliline comments 
+string index starts with 0 | left index -- count from 0
+right index -- count from -1 
+slicing : -- all</t>
+  </si>
+  <si>
+    <t>forward slicing | backward slicing | step slicing 
+forward index | backward index 
+python type casting | other datatypes to int ( complex &amp; text string ) 
+other datatype to float ( except complex &amp; text string)  
+other datatype to bool ( no issue at all )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">framework -- collection of packages 
+packages -- collection of modules | modules - collection of function 
+function -- collection of statement 
+math module </t>
+  </si>
+  <si>
+    <t xml:space="preserve">inpute() eval | </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuple - immutable ( we cant change ) values once we define () 
+tuple has indexing , slicing, count will works 
+set -- {} -- dict | {1, 2, 3} -- set set function indexing &amp; slicing not allowed 
+duplicates are not allowed in set 
+add() vs append() -- add the value randomly, append the value at last 
+copy() - pop() -- remove elemnt random from set , use mention argument inside the function then it works | remove() vs discard() -- remove the elemnet from the set &amp;  discard never through an error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">set operation -- intersection(&amp;), union(|), diffrnece(-) , symmetric differnece ^  
+parameter tunning -- system given parameter |Hyperparameter -- user change the system parameter as per user requirment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">format of the dict is keys:values 
+keys cannot be duplicate but values can be duplicates
+dictionary is mutable |  
+fromkeys(). Update() range() | range() we can pass max 3 argument 
+1st one start , end, step  | we discussed every concept of datastructure 
+numpy introduction | numpy we have many functionality 256 funcation 
+np.arange() -- arange the value betwnee the interval 
+np.arange() -- 3 argument |1d , 2d vs nd | numpy -- whihc handles nd array 
+np.zeros() -- by default flaot 0, np.ones()  bydefaul it prints float 1 | if you need integer then we must need to hypereparmeter tunning |np.random.rand (3) -- 3 random float number will generate
+np.random.randint(3) --  generate random int between 0-3 (0-, 1, 2) </t>
+  </si>
+  <si>
+    <t>Kaggle</t>
+  </si>
+  <si>
+    <t>IMDB movie data set analysis</t>
+  </si>
+  <si>
+    <t>Gradio + Functions</t>
+  </si>
+  <si>
+    <t>Python function + matplotlib | intro to gradio (another frontend library)</t>
+  </si>
+  <si>
+    <t>EDA-1</t>
+  </si>
+  <si>
+    <t>EDA-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pandas, DataFrame inspection, Data Cleaning, Regex patterns </t>
+  </si>
+  <si>
+    <t>Data cleaning (copy protection, dtype fixing, drop irrelevant columns), univariate analysis (histplot, countplot), bivariate analysis (boxplot, lmplot, barplot), groupby aggregation, get_dummies encoding — matplotlib OOP style (fig/ax skeleton), seaborn with ax=ax</t>
+  </si>
+  <si>
+    <t>Numpy + Pandas Revision</t>
+  </si>
+  <si>
+    <t>Array creation, slicing, axis-wise aggregations (sum/min/max/mean), cumsum, dot product, np.vectorize, np.save/load, image as array, CSV loading, feature extraction with .apply(), regex on columns, EDA (describe/info/value_counts), conditional filtering, string cleaning</t>
   </si>
 </sst>
 </file>
@@ -760,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
@@ -775,7 +764,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -790,7 +779,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -801,13 +790,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="54" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -818,13 +807,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -832,16 +821,16 @@
         <v>46085</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -849,16 +838,16 @@
         <v>46086</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -866,16 +855,16 @@
         <v>46087</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -883,13 +872,13 @@
         <v>46090</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="108" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -897,10 +886,10 @@
         <v>46091</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.25">
@@ -911,13 +900,13 @@
         <v>46092</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -925,10 +914,10 @@
         <v>46093</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="108" x14ac:dyDescent="0.25">
@@ -939,10 +928,10 @@
         <v>46094</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="126" x14ac:dyDescent="0.25">
@@ -953,13 +942,13 @@
         <v>46097</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="108" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="72" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -967,13 +956,13 @@
         <v>46098</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="72" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -981,10 +970,10 @@
         <v>46099</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="144" x14ac:dyDescent="0.25">
@@ -995,13 +984,13 @@
         <v>46101</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="144" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1009,13 +998,13 @@
         <v>46104</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="108" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="54" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1023,10 +1012,10 @@
         <v>46105</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="198" x14ac:dyDescent="0.25">
@@ -1037,10 +1026,10 @@
         <v>46106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
@@ -1051,10 +1040,10 @@
         <v>46107</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="180" x14ac:dyDescent="0.25">
@@ -1065,10 +1054,10 @@
         <v>46108</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="162" x14ac:dyDescent="0.25">
@@ -1079,10 +1068,10 @@
         <v>46111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="144" x14ac:dyDescent="0.25">
@@ -1093,10 +1082,10 @@
         <v>46112</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="126" x14ac:dyDescent="0.25">
@@ -1107,10 +1096,10 @@
         <v>46113</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="162" x14ac:dyDescent="0.25">
@@ -1121,10 +1110,10 @@
         <v>46114</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="108" x14ac:dyDescent="0.25">
@@ -1135,10 +1124,10 @@
         <v>46115</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1149,10 +1138,10 @@
         <v>46116</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1163,10 +1152,10 @@
         <v>46118</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="90" x14ac:dyDescent="0.25">
@@ -1177,10 +1166,10 @@
         <v>46119</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="54" x14ac:dyDescent="0.25">
@@ -1191,10 +1180,80 @@
         <v>46120</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46121</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46122</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="54" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46125</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46126</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="54" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report.xlsx
+++ b/Daily_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data_Science\01_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4303BC-AF66-4D46-85E9-FA3C532B2B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81B12C3-F4B7-41ED-B773-3D59EC651390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -349,6 +349,39 @@
   </si>
   <si>
     <t>Array creation, slicing, axis-wise aggregations (sum/min/max/mean), cumsum, dot product, np.vectorize, np.save/load, image as array, CSV loading, feature extraction with .apply(), regex on columns, EDA (describe/info/value_counts), conditional filtering, string cleaning</t>
+  </si>
+  <si>
+    <t>Data Visualization-2</t>
+  </si>
+  <si>
+    <t>Data Visualization-1</t>
+  </si>
+  <si>
+    <t>seaborn, matplotlib, histplot, kdeplot, countplot, barplot</t>
+  </si>
+  <si>
+    <t>boxplot, violinplot, stripplot, scatterplot, regplot, heatmap, pairplot, FacetGrid</t>
+  </si>
+  <si>
+    <t>SQL-1</t>
+  </si>
+  <si>
+    <t>SQL-2</t>
+  </si>
+  <si>
+    <t>MYSql shell, workbernch into, show db, create db, create table, insert record, insert multiple records, see the tables, see the specific table content, see the specific attributes</t>
+  </si>
+  <si>
+    <t>sum, average, count, asc desc, wild card, like %, joins: inner; outer; cross; left; right</t>
+  </si>
+  <si>
+    <t>EDA-Pro (Project)</t>
+  </si>
+  <si>
+    <t>pandas, numpy, matplotlib, streamlit</t>
+  </si>
+  <si>
+    <t>weasyPrint, pytest, type hints, google style docstrings, OOP, git</t>
   </si>
 </sst>
 </file>
@@ -749,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
@@ -1256,6 +1289,87 @@
         <v>71</v>
       </c>
     </row>
+    <row r="35" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46128</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46129</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46132</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46133</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46134</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46135</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
